--- a/tests/fixtures/messy/skewed.xlsx
+++ b/tests/fixtures/messy/skewed.xlsx
@@ -775,7 +775,7 @@
         <v>INV-2026015</v>
       </c>
       <c r="B17" t="str">
-        <v>Globex GmbH</v>
+        <v>Müller GmbH</v>
       </c>
       <c r="C17" s="1">
         <v>46079</v>
@@ -1580,7 +1580,7 @@
         <v>INV-2026015</v>
       </c>
       <c r="B17" t="str">
-        <v>Globex GmbH</v>
+        <v>Müller GmbH</v>
       </c>
       <c r="D17" s="1">
         <v>46079</v>
@@ -1833,7 +1833,7 @@
         <v>INV-2026026</v>
       </c>
       <c r="B28" t="str">
-        <v>Globex GmbH</v>
+        <v>Müller GmbH</v>
       </c>
       <c r="C28" s="1">
         <v>46069</v>
@@ -1925,7 +1925,7 @@
         <v>INV-2026030</v>
       </c>
       <c r="B32" t="str">
-        <v>Globex GmbH</v>
+        <v>Müller GmbH</v>
       </c>
       <c r="C32" s="1">
         <v>46028</v>
